--- a/Employee_Reports_wi52/Lemuel Celeste Anacleto Q0150.xlsx
+++ b/Employee_Reports_wi52/Lemuel Celeste Anacleto Q0150.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -717,11 +717,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -766,11 +766,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-151</v>
+        <v>-159</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-152</v>
+        <v>-160</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -913,11 +913,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-137</v>
+        <v>-145</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -962,11 +962,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1011,11 +1011,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1146,11 +1146,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1195,11 +1195,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1244,11 +1244,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1281,11 +1281,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1318,11 +1318,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1367,11 +1367,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1416,11 +1416,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1465,11 +1465,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1502,11 +1502,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1530,20 +1530,20 @@
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>02-Jul-2025</t>
+          <t>26-Aug-2026</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>02-Jul-2027</t>
+          <t>25-Aug-2028</t>
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>316</v>
+        <v>728</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1576,11 +1576,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
